--- a/data/trans_dic/P33_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,41; 29,77</t>
+          <t>24,24; 29,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,53; 38,21</t>
+          <t>31,49; 37,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,57; 33,01</t>
+          <t>26,37; 33,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,78; 37,32</t>
+          <t>28,78; 35,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,13; 37,18</t>
+          <t>31,67; 36,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,51; 46,01</t>
+          <t>40,62; 46,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 43,19</t>
+          <t>36,84; 43,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,49; 42,87</t>
+          <t>37,11; 42,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,19; 33,03</t>
+          <t>29,16; 33,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,72; 41,73</t>
+          <t>37,54; 41,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,44; 37,97</t>
+          <t>33,22; 37,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,09; 39,55</t>
+          <t>34,43; 39,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,78</t>
+          <t>12,53; 16,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,49; 24,29</t>
+          <t>20,42; 24,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,94; 23,58</t>
+          <t>19,67; 23,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 24,03</t>
+          <t>21,44; 25,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 19,87</t>
+          <t>15,91; 19,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,66; 30,04</t>
+          <t>25,73; 29,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,01; 26,83</t>
+          <t>22,99; 27,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,87; 51,52</t>
+          <t>26,67; 30,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,63; 17,23</t>
+          <t>14,58; 17,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,34; 26,5</t>
+          <t>23,37; 26,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,84; 24,7</t>
+          <t>21,83; 24,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 38,73</t>
+          <t>24,42; 27,13</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 19,95</t>
+          <t>13,29; 19,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,0; 27,23</t>
+          <t>18,58; 26,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,13; 24,53</t>
+          <t>17,21; 24,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,59; 28,29</t>
+          <t>19,12; 26,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 20,18</t>
+          <t>13,58; 20,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 22,82</t>
+          <t>15,39; 22,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,0; 25,04</t>
+          <t>17,98; 25,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,63; 30,74</t>
+          <t>24,69; 30,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,35; 18,83</t>
+          <t>14,19; 19,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,03; 23,49</t>
+          <t>18,17; 23,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 23,71</t>
+          <t>18,57; 23,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,17; 28,23</t>
+          <t>22,71; 27,39</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>27,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,19; 20,02</t>
+          <t>17,16; 20,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,22; 27,35</t>
+          <t>24,47; 27,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,88; 24,8</t>
+          <t>21,77; 24,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,43</t>
+          <t>22,93; 26,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,67; 25,58</t>
+          <t>22,68; 25,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,01; 34,18</t>
+          <t>30,91; 34,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,85; 30,13</t>
+          <t>26,98; 30,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,6; 48,26</t>
+          <t>29,31; 31,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,39; 22,39</t>
+          <t>20,32; 22,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 30,44</t>
+          <t>28,27; 30,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,84; 27,08</t>
+          <t>24,92; 26,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,59; 35,7</t>
+          <t>26,68; 28,67</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>167398</t>
+          <t>181474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>289193</t>
+          <t>312774</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>456592</t>
+          <t>494249</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>248868; 303479</t>
+          <t>247060; 303772</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305610; 370354</t>
+          <t>305243; 367730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199904; 248350</t>
+          <t>198386; 248508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148828; 186481</t>
+          <t>161533; 201994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>420360; 486434</t>
+          <t>414303; 481658</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>540738; 614118</t>
+          <t>542187; 619852</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>360273; 425947</t>
+          <t>363312; 429676</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>270303; 309108</t>
+          <t>291667; 334916</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>679345; 768860</t>
+          <t>678658; 772537</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>869079; 961364</t>
+          <t>864890; 963907</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>581342; 660030</t>
+          <t>577467; 659671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>428401; 482781</t>
+          <t>463895; 528291</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>456643</t>
+          <t>500185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>740148</t>
+          <t>598248</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1196791</t>
+          <t>1098434</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204493; 262872</t>
+          <t>208599; 266608</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>400898; 475171</t>
+          <t>399492; 477322</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>413084; 488574</t>
+          <t>407561; 486243</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>285065; 531389</t>
+          <t>461737; 543254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>252787; 312647</t>
+          <t>250323; 309986</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>449525; 526146</t>
+          <t>450601; 525037</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>456045; 531837</t>
+          <t>455716; 538766</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>562844; 1120959</t>
+          <t>560917; 635083</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>473666; 557866</t>
+          <t>472199; 558192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>865284; 982402</t>
+          <t>866657; 982313</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>885371; 1001127</t>
+          <t>884936; 993938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>988106; 1698985</t>
+          <t>1039649; 1155127</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149923</t>
+          <t>157141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>180428</t>
+          <t>200659</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>330351</t>
+          <t>357800</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>72926; 108734</t>
+          <t>72398; 108849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91404; 131042</t>
+          <t>89420; 129449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93697; 134126</t>
+          <t>94123; 135054</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125075; 180577</t>
+          <t>134128; 182648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63647; 95971</t>
+          <t>64560; 96008</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68419; 104662</t>
+          <t>70577; 105272</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98828; 137485</t>
+          <t>98737; 138300</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161158; 201078</t>
+          <t>179751; 223520</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>146451; 192102</t>
+          <t>144769; 196471</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169430; 220721</t>
+          <t>170723; 224285</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207715; 259838</t>
+          <t>203536; 259952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>299537; 364842</t>
+          <t>324619; 391525</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>773965</t>
+          <t>838801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1209769</t>
+          <t>1111682</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1983734</t>
+          <t>1950483</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>555227; 646675</t>
+          <t>554047; 649763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>825151; 931673</t>
+          <t>833685; 937682</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>737411; 835820</t>
+          <t>733694; 828582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>606230; 851719</t>
+          <t>783430; 891540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>760929; 858862</t>
+          <t>761366; 861081</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1099257; 1211679</t>
+          <t>1095827; 1212981</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>944423; 1059814</t>
+          <t>949138; 1056194</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1051180; 1713739</t>
+          <t>1060208; 1156609</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1342973; 1474587</t>
+          <t>1338686; 1468943</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1950651; 2116312</t>
+          <t>1964970; 2120577</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1710968; 1865232</t>
+          <t>1716780; 1854682</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1765405; 2463115</t>
+          <t>1876999; 2016892</t>
         </is>
       </c>
     </row>
